--- a/engine/tmgh_study/TMGH_Valuation_Model_10092026.xlsx
+++ b/engine/tmgh_study/TMGH_Valuation_Model_10092026.xlsx
@@ -2295,7 +2295,7 @@
         </is>
       </c>
       <c r="B7" s="13" t="n">
-        <v>0.3710320302096666</v>
+        <v>0.3256539205036353</v>
       </c>
     </row>
     <row r="8">
@@ -2305,7 +2305,7 @@
         </is>
       </c>
       <c r="B8" s="13" t="n">
-        <v>0.3341014637211595</v>
+        <v>0.3098095713981506</v>
       </c>
     </row>
     <row r="9">
@@ -2798,7 +2798,7 @@
         </is>
       </c>
       <c r="B17" s="13" t="n">
-        <v>0.3573828894703562</v>
+        <v>0.3155765623218869</v>
       </c>
     </row>
     <row r="18">
@@ -2878,14 +2878,14 @@
         </is>
       </c>
       <c r="B3" s="9" t="n">
-        <v>3.33274603069955</v>
+        <v>4.19372149068249</v>
       </c>
       <c r="C3" s="9" t="n">
-        <v>12.64818881769384</v>
+        <v>14.11260456761903</v>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>return on equity of 16.7% against a cost of equity of 37.1%</t>
+          <t>return on equity of 16.7% against a cost of equity of 32.6%</t>
         </is>
       </c>
     </row>
@@ -2896,10 +2896,10 @@
         </is>
       </c>
       <c r="B4" s="9" t="n">
-        <v>15.46564175092172</v>
+        <v>18.57572105502225</v>
       </c>
       <c r="C4" s="9" t="n">
-        <v>23.80326205675117</v>
+        <v>27.421482628649</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>

--- a/engine/tmgh_study/TMGH_Valuation_Model_10092026.xlsx
+++ b/engine/tmgh_study/TMGH_Valuation_Model_10092026.xlsx
@@ -33,7 +33,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="165" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="0.000000"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -3897,7 +3897,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -4232,136 +4232,173 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
+          <t>Cost of capital, this year's forward rate</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="n">
+        <v>0.3155765623218869</v>
+      </c>
+      <c r="C9" s="15" t="n">
+        <v>0.2702845796487516</v>
+      </c>
+      <c r="D9" s="15" t="n">
+        <v>0.2340509935102434</v>
+      </c>
+      <c r="E9" s="15" t="n">
+        <v>0.2068758039063623</v>
+      </c>
+      <c r="F9" s="15" t="n">
+        <v>0.1887590108371082</v>
+      </c>
+      <c r="G9" s="15" t="n">
+        <v>0.1887590108371082</v>
+      </c>
+      <c r="H9" s="15" t="n">
+        <v>0.1887590108371082</v>
+      </c>
+      <c r="I9" s="15" t="n">
+        <v>0.1887590108371082</v>
+      </c>
+      <c r="J9" s="15" t="n">
+        <v>0.1887590108371082</v>
+      </c>
+      <c r="K9" s="15" t="n">
+        <v>0.1887590108371082</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
           <t>Discount factor</t>
         </is>
       </c>
-      <c r="B9" s="19">
-        <f>1/(1+'Summary'!$B$14)^1</f>
-        <v/>
-      </c>
-      <c r="C9" s="19">
-        <f>1/(1+'Summary'!$B$14)^2</f>
-        <v/>
-      </c>
-      <c r="D9" s="19">
-        <f>1/(1+'Summary'!$B$14)^3</f>
-        <v/>
-      </c>
-      <c r="E9" s="19">
-        <f>1/(1+'Summary'!$B$14)^4</f>
-        <v/>
-      </c>
-      <c r="F9" s="19">
-        <f>1/(1+'Summary'!$B$14)^5</f>
-        <v/>
-      </c>
-      <c r="G9" s="19">
-        <f>1/(1+'Summary'!$B$14)^6</f>
-        <v/>
-      </c>
-      <c r="H9" s="19">
-        <f>1/(1+'Summary'!$B$14)^7</f>
-        <v/>
-      </c>
-      <c r="I9" s="19">
-        <f>1/(1+'Summary'!$B$14)^8</f>
-        <v/>
-      </c>
-      <c r="J9" s="19">
-        <f>1/(1+'Summary'!$B$14)^9</f>
-        <v/>
-      </c>
-      <c r="K9" s="19">
-        <f>1/(1+'Summary'!$B$14)^10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="B10" s="19">
+        <f>1/(1+B9)</f>
+        <v/>
+      </c>
+      <c r="C10" s="19">
+        <f>B10/(1+C9)</f>
+        <v/>
+      </c>
+      <c r="D10" s="19">
+        <f>C10/(1+D9)</f>
+        <v/>
+      </c>
+      <c r="E10" s="19">
+        <f>D10/(1+E9)</f>
+        <v/>
+      </c>
+      <c r="F10" s="19">
+        <f>E10/(1+F9)</f>
+        <v/>
+      </c>
+      <c r="G10" s="19">
+        <f>F10/(1+G9)</f>
+        <v/>
+      </c>
+      <c r="H10" s="19">
+        <f>G10/(1+H9)</f>
+        <v/>
+      </c>
+      <c r="I10" s="19">
+        <f>H10/(1+I9)</f>
+        <v/>
+      </c>
+      <c r="J10" s="19">
+        <f>I10/(1+J9)</f>
+        <v/>
+      </c>
+      <c r="K10" s="19">
+        <f>J10/(1+K9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>Present value</t>
         </is>
       </c>
-      <c r="B10" s="8">
-        <f>B8*B9</f>
-        <v/>
-      </c>
-      <c r="C10" s="8">
-        <f>C8*C9</f>
-        <v/>
-      </c>
-      <c r="D10" s="8">
-        <f>D8*D9</f>
-        <v/>
-      </c>
-      <c r="E10" s="8">
-        <f>E8*E9</f>
-        <v/>
-      </c>
-      <c r="F10" s="8">
-        <f>F8*F9</f>
-        <v/>
-      </c>
-      <c r="G10" s="8">
-        <f>G8*G9</f>
-        <v/>
-      </c>
-      <c r="H10" s="8">
-        <f>H8*H9</f>
-        <v/>
-      </c>
-      <c r="I10" s="8">
-        <f>I8*I9</f>
-        <v/>
-      </c>
-      <c r="J10" s="8">
-        <f>J8*J9</f>
-        <v/>
-      </c>
-      <c r="K10" s="8">
-        <f>K8*K9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="B11" s="8">
+        <f>B8*B10</f>
+        <v/>
+      </c>
+      <c r="C11" s="8">
+        <f>C8*C10</f>
+        <v/>
+      </c>
+      <c r="D11" s="8">
+        <f>D8*D10</f>
+        <v/>
+      </c>
+      <c r="E11" s="8">
+        <f>E8*E10</f>
+        <v/>
+      </c>
+      <c r="F11" s="8">
+        <f>F8*F10</f>
+        <v/>
+      </c>
+      <c r="G11" s="8">
+        <f>G8*G10</f>
+        <v/>
+      </c>
+      <c r="H11" s="8">
+        <f>H8*H10</f>
+        <v/>
+      </c>
+      <c r="I11" s="8">
+        <f>I8*I10</f>
+        <v/>
+      </c>
+      <c r="J11" s="8">
+        <f>J8*J10</f>
+        <v/>
+      </c>
+      <c r="K11" s="8">
+        <f>K8*K10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>Sum of the explicit years</t>
         </is>
       </c>
-      <c r="B12" s="17">
-        <f>SUM(B10:K10)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>Order book still unconverted, present value</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="n">
-        <v>20701.71014497908</v>
+      <c r="B13" s="17">
+        <f>SUM(B11:K11)</f>
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
+          <t>Order book still unconverted, present value</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="n">
+        <v>20701.71014497908</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
           <t>Recurring businesses beyond the window, present value</t>
         </is>
       </c>
-      <c r="B14" s="7" t="n">
+      <c r="B15" s="7" t="n">
         <v>39398.8589185091</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="11" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t>Enterprise value</t>
         </is>
       </c>
-      <c r="B15" s="17">
-        <f>B12+B13+B14</f>
+      <c r="B16" s="17">
+        <f>B13+B14+B15</f>
         <v/>
       </c>
     </row>

--- a/engine/tmgh_study/TMGH_Valuation_Model_10092026.xlsx
+++ b/engine/tmgh_study/TMGH_Valuation_Model_10092026.xlsx
@@ -507,7 +507,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Egyptian Exchange · TMGH · Egyptian pounds · 2026-09-02</t>
+          <t>Egyptian Exchange · TMGH · Egyptian pounds · 2026-09-10</t>
         </is>
       </c>
     </row>
@@ -3346,7 +3346,7 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  reference: minority at book</t>
+          <t xml:space="preserve">  reference: minority at book — NOT deducted below</t>
         </is>
       </c>
       <c r="B13" s="7" t="n">
@@ -3360,7 +3360,7 @@
         </is>
       </c>
       <c r="B14" s="17">
-        <f>B11+B13</f>
+        <f>B11+B12</f>
         <v/>
       </c>
     </row>

--- a/engine/tmgh_study/TMGH_Valuation_Model_10092026.xlsx
+++ b/engine/tmgh_study/TMGH_Valuation_Model_10092026.xlsx
@@ -2040,10 +2040,10 @@
         <v>0.2209793469145113</v>
       </c>
       <c r="B2" s="9" t="n">
-        <v>274.3133452381433</v>
+        <v>352.6692812553042</v>
       </c>
       <c r="C2" s="9" t="n">
-        <v>202.3111709138331</v>
+        <v>282.8696056955822</v>
       </c>
       <c r="D2" s="10">
         <f>B2/'Summary'!$B$2-1</f>
@@ -2055,10 +2055,10 @@
         <v>0.2609793469145114</v>
       </c>
       <c r="B3" s="9" t="n">
-        <v>180.4220469149492</v>
+        <v>198.3298111919148</v>
       </c>
       <c r="C3" s="9" t="n">
-        <v>111.5280800180366</v>
+        <v>129.4588867429611</v>
       </c>
       <c r="D3" s="10">
         <f>B3/'Summary'!$B$2-1</f>
@@ -2070,10 +2070,10 @@
         <v>0.2809793469145113</v>
       </c>
       <c r="B4" s="9" t="n">
-        <v>157.5353184931988</v>
+        <v>169.3690531270592</v>
       </c>
       <c r="C4" s="9" t="n">
-        <v>91.58878529132585</v>
+        <v>102.8840693329291</v>
       </c>
       <c r="D4" s="10">
         <f>B4/'Summary'!$B$2-1</f>
@@ -2085,10 +2085,10 @@
         <v>0.3009793469145113</v>
       </c>
       <c r="B5" s="9" t="n">
-        <v>140.7427369629646</v>
+        <v>149.24258044733</v>
       </c>
       <c r="C5" s="9" t="n">
-        <v>78.15638483556853</v>
+        <v>85.76847496278396</v>
       </c>
       <c r="D5" s="10">
         <f>B5/'Summary'!$B$2-1</f>
@@ -2100,10 +2100,10 @@
         <v>0.3209793469145114</v>
       </c>
       <c r="B6" s="9" t="n">
-        <v>127.7671355698158</v>
+        <v>134.1948653558038</v>
       </c>
       <c r="C6" s="9" t="n">
-        <v>68.72099226941695</v>
+        <v>74.05750806663541</v>
       </c>
       <c r="D6" s="10">
         <f>B6/'Summary'!$B$2-1</f>
@@ -2115,10 +2115,10 @@
         <v>0.3409793469145113</v>
       </c>
       <c r="B7" s="9" t="n">
-        <v>117.3925236932185</v>
+        <v>122.4250383939514</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>61.91266790077783</v>
+        <v>65.7499076078301</v>
       </c>
       <c r="D7" s="10">
         <f>B7/'Summary'!$B$2-1</f>
@@ -2130,10 +2130,10 @@
         <v>0.3809793469145114</v>
       </c>
       <c r="B8" s="9" t="n">
-        <v>101.8018594384564</v>
+        <v>105.1074662293701</v>
       </c>
       <c r="C8" s="9" t="n">
-        <v>53.17272021775515</v>
+        <v>55.25296255944607</v>
       </c>
       <c r="D8" s="10">
         <f>B8/'Summary'!$B$2-1</f>
@@ -2157,7 +2157,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="9" t="n">
-        <v>71.89462109656567</v>
+        <v>79.50601029726216</v>
       </c>
     </row>
     <row r="12">
@@ -2165,7 +2165,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="9" t="n">
-        <v>100.3476984105075</v>
+        <v>108.1058848211029</v>
       </c>
     </row>
     <row r="13">
@@ -2173,7 +2173,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="9" t="n">
-        <v>121.6024859971885</v>
+        <v>129.596545496059</v>
       </c>
     </row>
     <row r="14">
@@ -2181,7 +2181,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="9" t="n">
-        <v>138.2321539592412</v>
+        <v>146.5041022442187</v>
       </c>
     </row>
     <row r="15">
@@ -2189,7 +2189,7 @@
         <v>16</v>
       </c>
       <c r="B15" s="9" t="n">
-        <v>151.6618179308157</v>
+        <v>160.2278760989781</v>
       </c>
     </row>
     <row r="16">
@@ -2197,7 +2197,7 @@
         <v>20</v>
       </c>
       <c r="B16" s="9" t="n">
-        <v>172.0973110694273</v>
+        <v>181.2471576629438</v>
       </c>
     </row>
   </sheetData>
@@ -2660,17 +2660,17 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>273165.6735498477</v>
+        <v>294735.9295708061</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>284848.6133382954</v>
+        <v>301894.2350051377</v>
       </c>
       <c r="D7" s="9">
         <f>C7/$B$3</f>
         <v/>
       </c>
       <c r="E7" s="9" t="n">
-        <v>138.2118498264229</v>
+        <v>148.6795256781154</v>
       </c>
       <c r="F7" s="10">
         <f>D7/$B$2-1</f>
@@ -2684,17 +2684,17 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>113830.8979970636</v>
+        <v>133147.9677800082</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>158936.324684648</v>
+        <v>174201.3944599967</v>
       </c>
       <c r="D8" s="9">
         <f>C8/$B$3</f>
         <v/>
       </c>
       <c r="E8" s="9" t="n">
-        <v>60.88941189299415</v>
+        <v>70.26365504967801</v>
       </c>
       <c r="F8" s="10">
         <f>D8/$B$2-1</f>
@@ -2708,17 +2708,17 @@
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>279712.3680269551</v>
+        <v>301876.8924871483</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>290022.0557451334</v>
+        <v>307537.2905205962</v>
       </c>
       <c r="D9" s="9">
         <f>C9/$B$3</f>
         <v/>
       </c>
       <c r="E9" s="9" t="n">
-        <v>141.3888485426106</v>
+        <v>152.1449126908888</v>
       </c>
       <c r="F9" s="10">
         <f>D9/$B$2-1</f>
@@ -2732,17 +2732,17 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>116509.7472782852</v>
+        <v>136359.3313474745</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>161053.2514056767</v>
+        <v>176739.1338522656</v>
       </c>
       <c r="D10" s="9">
         <f>C10/$B$3</f>
         <v/>
       </c>
       <c r="E10" s="9" t="n">
-        <v>62.1894115733003</v>
+        <v>71.82207479367689</v>
       </c>
       <c r="F10" s="10">
         <f>D10/$B$2-1</f>
@@ -2808,7 +2808,7 @@
         </is>
       </c>
       <c r="B18" s="13" t="n">
-        <v>0.1886260236772954</v>
+        <v>0.1748066973261209</v>
       </c>
     </row>
   </sheetData>
@@ -2860,10 +2860,10 @@
         </is>
       </c>
       <c r="B2" s="9" t="n">
-        <v>60.88941189299415</v>
+        <v>70.26365504967801</v>
       </c>
       <c r="C2" s="9" t="n">
-        <v>141.3888485426106</v>
+        <v>152.1449126908888</v>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         </is>
       </c>
       <c r="B2" s="7" t="n">
-        <v>213065.1044863595</v>
+        <v>221850.0395304456</v>
       </c>
     </row>
     <row r="3">
@@ -3248,7 +3248,7 @@
         </is>
       </c>
       <c r="B3" s="7" t="n">
-        <v>20701.71014497908</v>
+        <v>24044.06135376647</v>
       </c>
     </row>
     <row r="4">
@@ -3258,7 +3258,7 @@
         </is>
       </c>
       <c r="B4" s="7" t="n">
-        <v>39398.8589185091</v>
+        <v>48841.82868659397</v>
       </c>
     </row>
     <row r="5">
@@ -3340,7 +3340,7 @@
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>-75610.96021155221</v>
+        <v>-80135.59456566832</v>
       </c>
     </row>
     <row r="13">
@@ -4239,31 +4239,31 @@
         <v>0.3155765623218869</v>
       </c>
       <c r="C9" s="15" t="n">
-        <v>0.2702845796487516</v>
+        <v>0.2653491059519036</v>
       </c>
       <c r="D9" s="15" t="n">
-        <v>0.2340509935102434</v>
+        <v>0.225167140855917</v>
       </c>
       <c r="E9" s="15" t="n">
-        <v>0.2068758039063623</v>
+        <v>0.1950306670339272</v>
       </c>
       <c r="F9" s="15" t="n">
-        <v>0.1887590108371082</v>
+        <v>0.1749396844859339</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>0.1887590108371082</v>
+        <v>0.1749396844859339</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>0.1887590108371082</v>
+        <v>0.1749396844859339</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>0.1887590108371082</v>
+        <v>0.1749396844859339</v>
       </c>
       <c r="J9" s="15" t="n">
-        <v>0.1887590108371082</v>
+        <v>0.1749396844859339</v>
       </c>
       <c r="K9" s="15" t="n">
-        <v>0.1887590108371082</v>
+        <v>0.1749396844859339</v>
       </c>
     </row>
     <row r="10">
@@ -4378,7 +4378,7 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>20701.71014497908</v>
+        <v>24044.06135376647</v>
       </c>
     </row>
     <row r="15">
@@ -4388,7 +4388,7 @@
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>39398.8589185091</v>
+        <v>48841.82868659397</v>
       </c>
     </row>
     <row r="16">
